--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.99260139414232</v>
+        <v>2.436297726548127</v>
       </c>
       <c r="D2" t="n">
-        <v>14.9257653364242</v>
+        <v>2.425436867168933</v>
       </c>
       <c r="E2" t="n">
-        <v>1.72913092439778</v>
+        <v>0.2809837752146394</v>
       </c>
       <c r="F2" t="n">
-        <v>1.812315057405035</v>
+        <v>0.2945011968283182</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.45086324293788</v>
+        <v>2.998265276977405</v>
       </c>
       <c r="D3" t="n">
-        <v>18.55039545123427</v>
+        <v>3.014439260825569</v>
       </c>
       <c r="E3" t="n">
-        <v>1.72913092439778</v>
+        <v>0.2809837752146394</v>
       </c>
       <c r="F3" t="n">
-        <v>1.812315057405035</v>
+        <v>0.2945011968283182</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
